--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487059_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487059_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. ALDA IRAOLA</t>
+          <t>J. ELOSEGUI OLANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7419</v>
+        <v>2.0137</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1111</v>
+        <v>1.989</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6308</v>
+        <v>0.0247</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2299</v>
+        <v>-0.1421</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.6116</v>
+        <v>0.1542</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8414</v>
+        <v>-0.2963</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.4387</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.3043</v>
+        <v>0.7554</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9943</v>
+        <v>0.6833</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4601</v>
+        <v>-1.5808</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3073</v>
+        <v>-0.6012</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1528</v>
+        <v>-0.9797</v>
       </c>
       <c r="P2" t="n">
-        <v>0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8401</v>
+        <v>0.3259</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8144</v>
+        <v>0.2644</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0258</v>
+        <v>0.0614</v>
       </c>
       <c r="V2" t="n">
         <v>0.2859</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5717</v>
+        <v>0.2859</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>U. PEREZ SANZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6149</v>
+        <v>1.42</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8041</v>
+        <v>1.1215</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1892</v>
+        <v>0.2985</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6011</v>
+        <v>-0.6882</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6656</v>
+        <v>-1.3166</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2667</v>
+        <v>0.6283</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0245</v>
+        <v>1.1532</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7036</v>
+        <v>-0.8489</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3209</v>
+        <v>2.0021</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.4234</v>
+        <v>-1.8415</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3691</v>
+        <v>-0.4677</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0542</v>
+        <v>-1.3738</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.193</v>
+        <v>1.7371</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1912</v>
+        <v>0.3711</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0801</v>
+        <v>-0.0317</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1111</v>
+        <v>0.4028</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9843</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>U. PEREZ SANZ</t>
+          <t>A. ALDA IRAOLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3337</v>
+        <v>0.9537</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0621</v>
+        <v>0.5102</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2717</v>
+        <v>0.4434</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6882</v>
+        <v>0.2299</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3166</v>
+        <v>-1.6116</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6283</v>
+        <v>1.8414</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1532</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8489</v>
+        <v>-1.3043</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0021</v>
+        <v>1.9943</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8415</v>
+        <v>-0.4601</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4677</v>
+        <v>-0.3073</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3738</v>
+        <v>-0.1528</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7371</v>
+        <v>0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2849</v>
+        <v>0.0519</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0912</v>
+        <v>0.2135</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3761</v>
+        <v>-0.1616</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ELOSEGUI OLANO</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0718</v>
+        <v>0.678</v>
       </c>
       <c r="E5" t="n">
-        <v>1.529</v>
+        <v>2.3223</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4572</v>
+        <v>-1.6443</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1421</v>
+        <v>0.6011</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1542</v>
+        <v>-0.6656</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2963</v>
+        <v>1.2667</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4387</v>
+        <v>4.0245</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7554</v>
+        <v>0.7036</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6833</v>
+        <v>3.3209</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5808</v>
+        <v>-3.4234</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6012</v>
+        <v>-1.3691</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9797</v>
+        <v>-2.0542</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5441</v>
+        <v>-0.193</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.616</v>
+        <v>1.2542</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1956</v>
+        <v>0.5982</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4204</v>
+        <v>0.656</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2859</v>
+        <v>-0.9843</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2859</v>
+        <v>-0.3704</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0055</v>
+        <v>0.3147</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3853</v>
+        <v>2.545</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3909</v>
+        <v>-2.2302</v>
       </c>
       <c r="G6" t="n">
         <v>0.6262</v>
@@ -922,13 +922,13 @@
         <v>1.5441</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0172</v>
+        <v>0.3374</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1507</v>
+        <v>0.0089</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1679</v>
+        <v>0.3285</v>
       </c>
       <c r="V6" t="n">
         <v>-1.228</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2076</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1171</v>
+        <v>-0.0169</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0906</v>
+        <v>-0.0638</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4925</v>
@@ -1000,13 +1000,13 @@
         <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2941</v>
+        <v>-0.1672</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1785</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1157</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>J. URTXULUTEGI NAVARRI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2078</v>
+        <v>-0.5668</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.1239</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5578</v>
+        <v>-0.4429</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8627</v>
+        <v>0.3701</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4347</v>
+        <v>0.1551</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2974</v>
+        <v>0.2149</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5776</v>
+        <v>2.3386</v>
       </c>
       <c r="K8" t="n">
-        <v>0.714</v>
+        <v>0.8898</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8636</v>
+        <v>1.4488</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7149</v>
+        <v>-1.9685</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1487</v>
+        <v>-0.7347</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5662</v>
+        <v>-1.2338</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1231</v>
+        <v>-1.158</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8602</v>
+        <v>-2.8951</v>
       </c>
       <c r="R8" t="n">
         <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7244</v>
+        <v>0.5493</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5169</v>
+        <v>0.1468</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2075</v>
+        <v>0.4025</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3281</v>
+        <v>-0.3281</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3281</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. URTXULUTEGI NAVARRI</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5728</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1834</v>
+        <v>-1.0065</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3894</v>
+        <v>0.3972</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3701</v>
+        <v>0.8627</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1551</v>
+        <v>-0.4347</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2149</v>
+        <v>1.2974</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3386</v>
+        <v>2.5776</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8898</v>
+        <v>0.714</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4488</v>
+        <v>1.8636</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9685</v>
+        <v>-1.7149</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7347</v>
+        <v>-1.1487</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2338</v>
+        <v>-0.5662</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.158</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8951</v>
+        <v>-3.8602</v>
       </c>
       <c r="R9" t="n">
         <v>1.7371</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5433</v>
+        <v>0.3229</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0873</v>
+        <v>0.276</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4561</v>
+        <v>0.0469</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3281</v>
+        <v>0.3281</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.614</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1701</v>
+        <v>-1.2574</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9917</v>
+        <v>-1.8915</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8216</v>
+        <v>0.6342</v>
       </c>
       <c r="G10" t="n">
         <v>-0.17</v>
@@ -1234,13 +1234,13 @@
         <v>0.772</v>
       </c>
       <c r="S10" t="n">
-        <v>0.158</v>
+        <v>0.0707</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1785</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3364</v>
+        <v>0.149</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0747</v>
+        <v>-1.5274</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.233</v>
+        <v>0.1269</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8418</v>
+        <v>-1.6544</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9022</v>
@@ -1312,13 +1312,13 @@
         <v>1.3511</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5236</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7733</v>
+        <v>-0.4134</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7502</v>
+        <v>-0.5628</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4894</v>
+        <v>-1.7091</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3036</v>
+        <v>-0.6839</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1858</v>
+        <v>-1.0252</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0002</v>
@@ -1390,13 +1390,13 @@
         <v>1.3511</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9175</v>
+        <v>-0.1372</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5803</v>
+        <v>0.0393</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3371</v>
+        <v>-0.1765</v>
       </c>
       <c r="V12" t="n">
         <v>0.0422</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9656000000000002</v>
+        <v>-0.3706999999999996</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2972</v>
+        <v>4.892200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.263</v>
+        <v>-5.2628</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7052</v>
@@ -1468,13 +1468,13 @@
         <v>15.4409</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4079</v>
+        <v>2.0027</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3506000000000001</v>
+        <v>0.9454000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0575</v>
+        <v>1.0573</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5983</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.408899999999999</v>
+        <v>8.7483</v>
       </c>
       <c r="E14" t="n">
-        <v>6.508</v>
+        <v>7.0088</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9008</v>
+        <v>1.7396</v>
       </c>
       <c r="G14" t="n">
         <v>9.595800000000001</v>
@@ -1546,13 +1546,13 @@
         <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.164</v>
+        <v>0.1755</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9082</v>
+        <v>-0.4075</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7442</v>
+        <v>0.5829</v>
       </c>
       <c r="V14" t="n">
         <v>0.3281</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. CAMARA</t>
+          <t>J. REINER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4951</v>
+        <v>3.9467</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7818</v>
+        <v>3.3358</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7133</v>
+        <v>0.6109</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0933</v>
+        <v>5.2039</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3678</v>
+        <v>2.632</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2745</v>
+        <v>2.5719</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5535</v>
+        <v>6.8314</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6338</v>
+        <v>3.0064</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9197</v>
+        <v>3.825</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4602</v>
+        <v>-1.6275</v>
       </c>
       <c r="N15" t="n">
-        <v>0.734</v>
+        <v>-0.3744</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.1942</v>
+        <v>-1.2531</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7371</v>
+        <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3246</v>
+        <v>-0.2994</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2586</v>
+        <v>-0.6005</v>
       </c>
       <c r="U15" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.301</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2702</v>
+        <v>-0.5717</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3704</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. REINER</t>
+          <t>L. CAMARA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5805</v>
+        <v>3.7538</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8351</v>
+        <v>2.8805</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7454</v>
+        <v>0.8733</v>
       </c>
       <c r="G16" t="n">
-        <v>5.2039</v>
+        <v>2.0933</v>
       </c>
       <c r="H16" t="n">
-        <v>2.632</v>
+        <v>3.3678</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5719</v>
+        <v>-1.2745</v>
       </c>
       <c r="J16" t="n">
-        <v>6.8314</v>
+        <v>3.5535</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0064</v>
+        <v>2.6338</v>
       </c>
       <c r="L16" t="n">
-        <v>3.825</v>
+        <v>0.9197</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6275</v>
+        <v>-1.4602</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3744</v>
+        <v>0.734</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2531</v>
+        <v>-2.1942</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5091</v>
+        <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6656</v>
+        <v>0.5833</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1012</v>
+        <v>0.3573</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4355</v>
+        <v>0.226</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5717</v>
+        <v>1.2702</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5717</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8822</v>
+        <v>0.1944</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2541</v>
+        <v>0.3528</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3719</v>
+        <v>-0.1584</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5202</v>
@@ -1780,13 +1780,13 @@
         <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3445</v>
+        <v>0.6567</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2731</v>
+        <v>0.3718</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0713</v>
+        <v>0.2849</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3281</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6647</v>
+        <v>-1.0385</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3162</v>
+        <v>-0.7168</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3485</v>
+        <v>-0.3217</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2328</v>
@@ -1858,13 +1858,13 @@
         <v>0.193</v>
       </c>
       <c r="S18" t="n">
-        <v>0.626</v>
+        <v>0.2522</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6081</v>
+        <v>0.2076</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2859</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3984</v>
+        <v>-2.2448</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4243</v>
+        <v>-1.3241</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9742</v>
+        <v>-0.9206</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9046</v>
@@ -1936,13 +1936,13 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3358</v>
+        <v>-0.1821</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0978</v>
+        <v>-0.0443</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7762</v>
+        <v>-2.3618</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9208</v>
+        <v>-0.7205</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8554</v>
+        <v>-1.6413</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9235</v>
@@ -2014,13 +2014,13 @@
         <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6597</v>
+        <v>-0.2452</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4614</v>
+        <v>-0.2611</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1983</v>
+        <v>0.0159</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2493</v>
+        <v>-3.4138</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8821</v>
+        <v>-1.5816</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3672</v>
+        <v>-1.8322</v>
       </c>
       <c r="G21" t="n">
         <v>-4.3937</v>
@@ -2092,13 +2092,13 @@
         <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4852</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7442</v>
+        <v>-0.4438</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.741</v>
+        <v>-0.2059</v>
       </c>
       <c r="V21" t="n">
         <v>0.8576</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3124</v>
+        <v>-5.2835</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5728</v>
+        <v>-3.9719</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7396</v>
+        <v>-1.3116</v>
       </c>
       <c r="G22" t="n">
         <v>-6.2128</v>
@@ -2170,13 +2170,13 @@
         <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3927</v>
+        <v>-0.3639</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7442</v>
+        <v>-0.1434</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6485</v>
+        <v>-0.2205</v>
       </c>
       <c r="V22" t="n">
         <v>0.3281</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9657000000000018</v>
+        <v>2.300799999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>5.262799999999999</v>
+        <v>5.263</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.2973</v>
+        <v>-2.962</v>
       </c>
       <c r="G23" t="n">
-        <v>2.705399999999999</v>
+        <v>2.705400000000003</v>
       </c>
       <c r="H23" t="n">
         <v>4.072699999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3673</v>
+        <v>-1.367300000000001</v>
       </c>
       <c r="J23" t="n">
         <v>19.7176</v>
@@ -2248,13 +2248,13 @@
         <v>13.5106</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4079</v>
+        <v>-0.07260000000000022</v>
       </c>
       <c r="T23" t="n">
         <v>-1.0574</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3507000000000001</v>
+        <v>0.9846</v>
       </c>
       <c r="V23" t="n">
         <v>1.5983</v>
